--- a/1375534_Cuenca_Lurin/_raw_reportes_xlsx/IDConfig_63323_completo.xlsx
+++ b/1375534_Cuenca_Lurin/_raw_reportes_xlsx/IDConfig_63323_completo.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R322ac0136d744512"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="Re1d65de820a2412d"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -174,7 +174,7 @@
       </x:c>
       <x:c s="" t="inlineStr">
         <x:is>
-          <x:t>Dpto: Lima / Prov: Huarochiri / Dist.: Antioquia</x:t>
+          <x:t>Dpto: Lima / Prov: Huarochirí / Dist.: Antioquia</x:t>
         </x:is>
       </x:c>
     </x:row>
